--- a/dnis.xlsx
+++ b/dnis.xlsx
@@ -1187,7 +1187,7 @@
     </row>
     <row r="2" spans="1:1">
       <c r="A2">
-        <v>12345678</v>
+        <v>12345679</v>
       </c>
     </row>
     <row r="3" spans="1:1">
